--- a/analysis/econometrics_outputs/contdid/Graficos/unemployment/dose/contdid_cosine_nearest_dose_att.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/unemployment/dose/contdid_cosine_nearest_dose_att.xlsx
@@ -488,10 +488,10 @@
         <v>-0.0411999666780739</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.0251398158125424</v>
+        <v>0.032416956731046</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -510,10 +510,10 @@
         <v>-0.0403416906127816</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.0229397564692809</v>
+        <v>0.0298189454223825</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -532,10 +532,10 @@
         <v>-0.0397766011162246</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.0215405953056218</v>
+        <v>0.0275532742221519</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -554,10 +554,10 @@
         <v>-0.0358938025935978</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.0128510224874457</v>
+        <v>0.0232522555544503</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -576,10 +576,10 @@
         <v>-0.0347300712873014</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.0105210685622872</v>
+        <v>0.0212245589796265</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -598,10 +598,10 @@
         <v>-0.033077949961137</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.00740020207714471</v>
+        <v>0.0201013055218921</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -620,10 +620,10 @@
         <v>-0.0312219222381235</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.00409719943731338</v>
+        <v>0.0189409343293298</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -642,10 +642,10 @@
         <v>-0.0300161944344751</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.00146032595242613</v>
+        <v>0.0177240170677004</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -664,10 +664,10 @@
         <v>-0.0300161944344751</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.00146032595242613</v>
+        <v>0.0177240170677004</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -686,10 +686,10 @@
         <v>-0.0289144753636849</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.000842705987562691</v>
+        <v>0.0177613288044761</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -708,10 +708,10 @@
         <v>-0.0267252576062756</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.00225646779348586</v>
+        <v>0.0175618863119178</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -730,10 +730,10 @@
         <v>-0.0260866331671829</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.00253976086461169</v>
+        <v>0.0173957186044552</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -752,10 +752,10 @@
         <v>-0.0240407049066993</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.00339926798069265</v>
+        <v>0.0181868707903345</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -774,10 +774,10 @@
         <v>-0.0228668335979598</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.00386117963336708</v>
+        <v>0.0184539577454813</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -796,10 +796,10 @@
         <v>-0.0204227654366671</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.002601859459787</v>
+        <v>0.0196110548063559</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -818,10 +818,10 @@
         <v>-0.0198309701176434</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.00187459898369633</v>
+        <v>0.0202524793602406</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -840,10 +840,10 @@
         <v>-0.0191894445154048</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.00110004157346259</v>
+        <v>0.0208493093016288</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -862,10 +862,10 @@
         <v>-0.0129179575135771</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.00639410872356871</v>
+        <v>0.0248633075812596</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -884,10 +884,10 @@
         <v>-0.00903145228068352</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.00999284558898528</v>
+        <v>0.0252363549240602</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -906,10 +906,10 @@
         <v>-0.00903145228068352</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.00999284558898528</v>
+        <v>0.0252363549240602</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -928,10 +928,10 @@
         <v>-0.00658368590481409</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.0120628359971448</v>
+        <v>0.025604287605809</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -950,10 +950,10 @@
         <v>-0.00345670416051495</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.0145061058089126</v>
+        <v>0.0259564545279474</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -972,10 +972,10 @@
         <v>-0.00267599471235895</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.0150829799192853</v>
+        <v>0.0258505715922382</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -994,10 +994,10 @@
         <v>0.00145703318186379</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.0179317809015157</v>
+        <v>0.0254027905140107</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1016,10 +1016,10 @@
         <v>0.00336033308312641</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.0191342866256561</v>
+        <v>0.0256757458159974</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1038,10 +1038,10 @@
         <v>0.00459437072267295</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.0198792897914549</v>
+        <v>0.0263000951527529</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1060,10 +1060,10 @@
         <v>0.013374004685353</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>0.0247919143288314</v>
+        <v>0.0250606816724165</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1082,10 +1082,10 @@
         <v>0.0170042744928597</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>0.0265159906631676</v>
+        <v>0.0250635678152884</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1104,10 +1104,10 @@
         <v>0.0182683225609035</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.0270765707664561</v>
+        <v>0.0248112713262386</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1126,10 +1126,10 @@
         <v>0.0195785140658029</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>0.0276368956084014</v>
+        <v>0.0250764725049797</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1148,10 +1148,10 @@
         <v>0.0213101156379897</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.0283460587093984</v>
+        <v>0.0254043301585083</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1170,10 +1170,10 @@
         <v>0.0249073447019737</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.0297102599926495</v>
+        <v>0.0249471337207218</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1192,10 +1192,10 @@
         <v>0.0328250855764866</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.0322404586266446</v>
+        <v>0.0251072962017621</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1214,10 +1214,10 @@
         <v>0.0347484436465961</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.0327661498886774</v>
+        <v>0.0256384390801879</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1236,10 +1236,10 @@
         <v>0.036501305942263</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.033217563077301</v>
+        <v>0.0248782584820598</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1258,10 +1258,10 @@
         <v>0.0391094377525145</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.0338428593485907</v>
+        <v>0.0243066537585726</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1280,10 +1280,10 @@
         <v>0.0405932671481982</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.0341751007855272</v>
+        <v>0.0238005429503694</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -1302,10 +1302,10 @@
         <v>0.0427049732865292</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.0346202456255782</v>
+        <v>0.0228892306430578</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -1324,10 +1324,10 @@
         <v>0.0430428694867927</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.0346885780807093</v>
+        <v>0.0226458674414035</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -1346,10 +1346,10 @@
         <v>0.051980133651615</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.0362457794675563</v>
+        <v>0.0225314337097689</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -1368,10 +1368,10 @@
         <v>0.0565012145269665</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.0358489011887398</v>
+        <v>0.0215805829832538</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -1390,10 +1390,10 @@
         <v>0.0574000211176677</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.0357389301889316</v>
+        <v>0.022320374292233</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -1412,10 +1412,10 @@
         <v>0.0595875812163132</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.0354573841693597</v>
+        <v>0.0223877382254708</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -1434,10 +1434,10 @@
         <v>0.060675865092446</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.0353093240562683</v>
+        <v>0.0226839879623849</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -1456,10 +1456,10 @@
         <v>0.0624002334871799</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>0.0350625927255204</v>
+        <v>0.0223852607730903</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -1478,10 +1478,10 @@
         <v>0.0698587500525278</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>0.0337695655666821</v>
+        <v>0.0228861109799401</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -1500,10 +1500,10 @@
         <v>0.0734991496787474</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>0.0329361021966937</v>
+        <v>0.0233168626527014</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -1522,10 +1522,10 @@
         <v>0.0778835004216455</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>0.0315804695376321</v>
+        <v>0.0226846033320791</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -1544,10 +1544,10 @@
         <v>0.0805396646588703</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>0.0303358028336072</v>
+        <v>0.0242562453279575</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -1566,10 +1566,10 @@
         <v>0.0815171333083529</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.0296627056099247</v>
+        <v>0.0242896357334051</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -1588,10 +1588,10 @@
         <v>0.0819484059903752</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.0292759386489848</v>
+        <v>0.0243341622972451</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -1610,10 +1610,10 @@
         <v>0.0819484059903752</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>0.0292759386489848</v>
+        <v>0.0243341622972451</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -1632,10 +1632,10 @@
         <v>0.0821290174642765</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>0.0290840320700319</v>
+        <v>0.0244795347654489</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -1654,10 +1654,10 @@
         <v>0.0824650234580637</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>0.0286410975957342</v>
+        <v>0.0242751200256125</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -1676,10 +1676,10 @@
         <v>0.0827564495409214</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>0.028017988966363</v>
+        <v>0.0247700779461131</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -1698,10 +1698,10 @@
         <v>0.0828149094395307</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>0.0277790013026551</v>
+        <v>0.0246304814210681</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -1720,10 +1720,10 @@
         <v>0.0825748645753026</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>0.0262989443564543</v>
+        <v>0.0246388789369539</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -1742,10 +1742,10 @@
         <v>0.0822709396901031</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>0.0257892854104192</v>
+        <v>0.0248928912352001</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -1764,10 +1764,10 @@
         <v>0.0814020964462061</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>0.0248119709573262</v>
+        <v>0.0256272678077815</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -1786,10 +1786,10 @@
         <v>0.0809390912179735</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>0.0244074757785025</v>
+        <v>0.0262710053903692</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -1808,10 +1808,10 @@
         <v>0.0766629101859129</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>0.0217978018058686</v>
+        <v>0.0237934470208326</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -1830,10 +1830,10 @@
         <v>0.0732211247895496</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>0.0197196512592093</v>
+        <v>0.0257058019011294</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -1852,10 +1852,10 @@
         <v>0.0716265959934091</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>0.0185600812894149</v>
+        <v>0.023934972267136</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -1874,10 +1874,10 @@
         <v>0.0667479330234857</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>0.015219033161489</v>
+        <v>0.0243686681712152</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -1896,10 +1896,10 @@
         <v>0.0640729910312174</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>0.0134906883875945</v>
+        <v>0.0236906104730188</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -1918,10 +1918,10 @@
         <v>0.0611865452753368</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>0.0127128327717849</v>
+        <v>0.0230028455271739</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -1940,10 +1940,10 @@
         <v>0.0589530081681956</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>0.0121399244932444</v>
+        <v>0.0228074374641342</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
@@ -1962,10 +1962,10 @@
         <v>0.0562706279378849</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>0.011479466459912</v>
+        <v>0.0247210900676954</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
@@ -1984,10 +1984,10 @@
         <v>0.0493433833465647</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>0.00988065046091754</v>
+        <v>0.0242196895860067</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
@@ -2006,10 +2006,10 @@
         <v>0.0468185476468588</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>0.00932693499212172</v>
+        <v>0.0243763176660433</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -2028,10 +2028,10 @@
         <v>0.0459048215690963</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>0.00912948415570215</v>
+        <v>0.0244525220510106</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -2050,10 +2050,10 @@
         <v>0.044931793371512</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>0.00892073140251282</v>
+        <v>0.0249918733336087</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -2072,10 +2072,10 @@
         <v>0.0429264810418985</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>0.0092999508771754</v>
+        <v>0.0265144047827515</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -2094,10 +2094,10 @@
         <v>0.0393733660959667</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>0.0113391258369856</v>
+        <v>0.0268831581033268</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -2116,10 +2116,10 @@
         <v>0.0356492598649665</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>0.011185118392898</v>
+        <v>0.0273887555176761</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
@@ -2138,10 +2138,10 @@
         <v>0.0305921503721086</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>0.00839202636595569</v>
+        <v>0.0288280992008628</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -2160,10 +2160,10 @@
         <v>0.0297776855230006</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>0.00789249758097138</v>
+        <v>0.0289269250361676</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -2182,10 +2182,10 @@
         <v>0.0259725215531481</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>0.00520524105457475</v>
+        <v>0.0294354024964099</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -2204,10 +2204,10 @@
         <v>0.0236831738451131</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>0.00425917119772297</v>
+        <v>0.0302637380674596</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
@@ -2226,10 +2226,10 @@
         <v>0.0230059831971409</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>0.00401613119261226</v>
+        <v>0.0318213947317214</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
@@ -2248,10 +2248,10 @@
         <v>0.0224697386787712</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>0.0038831575914223</v>
+        <v>0.0364148133889347</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
@@ -2270,10 +2270,10 @@
         <v>0.0224851229625041</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>0.0039862403661729</v>
+        <v>0.0366966006562407</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -2292,10 +2292,10 @@
         <v>0.0236443540037212</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>0.00537970622972663</v>
+        <v>0.0408267536853295</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -2314,10 +2314,10 @@
         <v>0.0267379835611827</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>0.00549667353165376</v>
+        <v>0.0415323986837794</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -2336,10 +2336,10 @@
         <v>0.0309646085610633</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>0.00582344670476936</v>
+        <v>0.0439482744617891</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -2358,10 +2358,10 @@
         <v>0.0341748814551585</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>0.00611532580681588</v>
+        <v>0.0436596583441225</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -2380,10 +2380,10 @@
         <v>0.0342749417147718</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>0.00612478596042554</v>
+        <v>0.0436308123246206</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -2402,10 +2402,10 @@
         <v>0.0497474914491983</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>0.00771853565110681</v>
+        <v>0.0461840959323318</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -2424,10 +2424,10 @@
         <v>0.0861105890262955</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>0.0117998572360622</v>
+        <v>0.0545777423302604</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -2446,10 +2446,10 @@
         <v>0.287842481269108</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>0.0194546444649233</v>
+        <v>0.0994179822905515</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>36.5003158704699</v>
+        <v>3.27663468750318</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
